--- a/data/PersonnelList.xlsx
+++ b/data/PersonnelList.xlsx
@@ -575,14 +575,10 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-30 15:20:48</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -987,14 +983,10 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-30 15:20:48</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1207,14 +1199,10 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-20 10:33:44</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1499,14 +1487,10 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-20 10:33:44</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1575,14 +1559,10 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-06-30 15:20:48</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1699,14 +1679,10 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-06-20 10:33:44</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">

--- a/data/PersonnelList.xlsx
+++ b/data/PersonnelList.xlsx
@@ -482,7 +482,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,7 +510,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -530,7 +538,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -554,7 +566,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -575,10 +591,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:53:25</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -602,7 +622,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -626,7 +650,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -650,7 +678,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -674,7 +706,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,7 +734,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -719,10 +759,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:53:14</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -746,7 +790,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -770,7 +818,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -794,7 +846,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,7 +874,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,7 +902,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -866,7 +930,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -890,7 +958,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -914,7 +986,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -938,7 +1014,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -962,7 +1042,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -986,7 +1070,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1010,7 +1098,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1034,7 +1126,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1058,7 +1154,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1082,7 +1182,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1106,7 +1210,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1127,10 +1235,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:53:14</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1154,7 +1266,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1178,7 +1294,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1202,7 +1322,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1226,7 +1350,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1250,7 +1378,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:53:14</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1274,7 +1406,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1298,7 +1434,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1322,7 +1462,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1346,7 +1490,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1370,7 +1518,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1394,7 +1546,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1418,7 +1574,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1442,7 +1602,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1466,7 +1630,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1490,7 +1658,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1514,7 +1686,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1538,7 +1714,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1562,7 +1742,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1586,7 +1770,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1610,7 +1798,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1634,7 +1826,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1658,7 +1854,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1682,7 +1882,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1706,7 +1910,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1730,7 +1938,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1754,7 +1966,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
